--- a/daily_matches/job_matches_2026-09-29.xlsx
+++ b/daily_matches/job_matches_2026-09-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Business Consultant - AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Docker, Kubernetes</t>
+          <t>Data Scientist, Generative AI, RAG, Athena, Kinesis, Docker, Git, Snowflake, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b982bc2ef3815e44</t>
+          <t>https://www.indeed.com/viewjob?jk=c96ed04a9d166985</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Advanced AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ERCOT/Electric Reliability Council of Texas</t>
+          <t>Relativity</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taylor, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions</t>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd0e00d31627020</t>
+          <t>https://www.indeed.com/viewjob?jk=423eda1e0efbb045</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Distributed Systems Engineer, Energy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Data Lake, FastAPI, Kubernetes, AKS, CI/CD, Terraform, Databricks</t>
+          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b6f2a27bb5dca4</t>
+          <t>https://www.indeed.com/viewjob?jk=5a63e864705cad81</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Docker, CI/CD, Git</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PySpark, Hadoop, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e3d7ad13472832</t>
+          <t>https://www.indeed.com/viewjob?jk=51a31aef3876037c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer Senior Consultant II</t>
+          <t>Python &amp; Java Full Stack Developer (AI-Assisted)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7614931d141812f</t>
+          <t>https://www.indeed.com/viewjob?jk=65877c8eb122e7ac</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III (AI/ML)</t>
+          <t>Forward Development Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>CrossCountry Consulting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Docker, Kubernetes, Git, PostgreSQL</t>
+          <t>AI Engineer, LangChain, RAG, Pinecone, Prompt Engineering, Data Lake, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd43da7937033d11</t>
+          <t>https://www.indeed.com/viewjob?jk=7425b7eaa6c55a6d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - App Experience</t>
+          <t>Senior Analytics Engineer, Enterprise Analytics</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HiveWatch</t>
+          <t>The Inland Real Estate Group of Companies, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
+          <t>RAG, Copilot, Synapse, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9778ba4147d2ed02</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1fbedd6c9d0d1c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate, Data &amp; Technology</t>
+          <t>Senior Analytics Engineer, Enterprise Analytics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>The Inland Real Estate Group of Companies, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Athena, Docker, Apache Airflow, Terraform, Git, Snowflake, Python</t>
+          <t>RAG, Copilot, Synapse, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125c48bf8c53a131</t>
+          <t>https://www.indeed.com/viewjob?jk=519dcdfdfb4bef2a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Analytics Engineer, Enterprise Analytics</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Builder Supply Link</t>
+          <t>The Inland Real Estate Group of Companies, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>West Orange, NJ, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, Copilot, Synapse, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=753a5119b1aa2067</t>
+          <t>https://www.indeed.com/viewjob?jk=de1d075b9f067a1b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Baker Hughes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Gemini, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Databricks, PySpark</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb55e308f3bed84</t>
+          <t>https://www.indeed.com/viewjob?jk=4a1910476c5d08e3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ZT Systems</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Git, Databricks, Kafka, PostgreSQL, MySQL, Python, SQL</t>
+          <t>Data Scientist, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724b45955d615a29</t>
+          <t>https://www.indeed.com/viewjob?jk=d94fb3ecd34b2c14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, Git, Databricks, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, MySQL, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b789d7b431d2dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=02324287df1f2770</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Data Engineer/AI Solution Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>W. L. Gore &amp; Associates</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Elkton, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02cd474395c7b916</t>
+          <t>https://www.indeed.com/viewjob?jk=4c7a8b75d558d86a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Senior SW Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dentsply Sirona</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50028acce61fae20</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3794a67a181956</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Databricks Engineer - Contractor (contract)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Data Lake, Snowflake, Databricks, PySpark, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57561f036d84d300</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f788a895458b3b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Vector Bidding Science</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>KBX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Copilot, PyTorch, BigQuery, Git, BigQuery, Python, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993432eef3ceee2d</t>
+          <t>https://www.indeed.com/viewjob?jk=d82ffb5eaa627d9d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Vector Bidding Science</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>KBX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Copilot, PyTorch, BigQuery, Git, BigQuery, Python, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cffd94dfe7503ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e7dd4a9a7ed2c5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse (EDW) Architect - OI State Government Solutions - Remote</t>
+          <t>Software Engineer III - AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Dataflow, CI/CD, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, Glue, Athena, Redshift, CI/CD, Terraform, Redshift, Python, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89e53d9ca8bf12e1</t>
+          <t>https://www.indeed.com/viewjob?jk=fca4cdbad781b6fe</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Anvilogic</t>
+          <t>RightsLine</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Kinesis, Terraform, Snowflake, MySQL, Python, SQL, R</t>
+          <t>LangChain, RAG, Copilot, Git, NoSQL, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,54 +1126,54 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905d183e2746c92f</t>
+          <t>https://www.indeed.com/viewjob?jk=355bd600a0ce4716</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Technology Consultant - Cloud &amp; Full Stack Engineer</t>
+          <t>Consultant or Senior Consultant, Technical Solutions</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>AVP, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
+          <t>RAG, Gemini, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f10e71883167c5f</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf1c610c653b6b3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Diabetes Association</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R</t>
+          <t>RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5989aaf1c5b0e5be</t>
+          <t>https://www.indeed.com/viewjob?jk=dba066468e1bd0ab</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ff5708d595f151</t>
+          <t>https://www.indeed.com/viewjob?jk=83646eeb4bc9897a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Support Engineer - Tooling &amp; Automation</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>THORN</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lemont, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, S3, Docker, Git, PostgreSQL, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d506486df6db83</t>
+          <t>https://www.indeed.com/viewjob?jk=1f00ff6ed18dfd67</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Maximo</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>National Grid</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Kubernetes, CI/CD, Terraform, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=810c7c9aefe11f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=b63bbe79a14f6024</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Advanced R&amp;D Engr/Scientist</t>
+          <t>Data Science Internship (Current PhD) - Summer 2027</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Solstice Advanced Materials</t>
+          <t>Neighbor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, NoSQL, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Athena, Redshift, AKS, Redshift, Python, SQL, R, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4640656b48b427b9</t>
+          <t>https://www.indeed.com/viewjob?jk=216ebd6cfdfcddb6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Scientist/Sr Data Scientist, Technical Operations</t>
+          <t>CCB Risk Program Associate</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, PySpark, Python, SQL, R, Java, Optimization</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Git, Hadoop, Python, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c5cf2f2be888c4</t>
+          <t>https://www.indeed.com/viewjob?jk=27157e509862847c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Reporting &amp; Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Kubernetes, CI/CD, Terraform, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216f035a5325c7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=575d748548b1953f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, AKS, CI/CD, GitHub Actions, Git, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e952d98de0a2f6da</t>
+          <t>https://www.indeed.com/viewjob?jk=8f9b69b4f17b5f1c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Junior Data Security Engineer</t>
+          <t>Senior Software Engineer, Enterprise AI Platform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, S3, BigQuery, AKS, CI/CD, Git, BigQuery, Python, R, Java</t>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0231b5b6e9bb14</t>
+          <t>https://www.indeed.com/viewjob?jk=37f37f938e18bf5a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Git, Python, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Snowflake, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69922eb033c76f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=41cb1e21fca446fa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Reporting &amp; Analytics</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Snowflake, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bccdb7a477decd</t>
+          <t>https://www.indeed.com/viewjob?jk=f54c5e3c17dace4d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Operations Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Anvilogic</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist, Data Lake, Terraform, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Snowflake, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b644fdfe443ca00d</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b78965e521bd63</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Site Reliability &amp; DevOps Engineer (Mid-Level) -Splunk, PageDuty</t>
+          <t>Data Analyst II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Education Analytics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LLaMA, Copilot, Docker, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05a2ff341b5f72cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4c4a90bc5d6ea3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer, 3D Data</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, MLflow, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9813030cd79e81ba</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc119467d5eb85a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>University of Pennsylvania</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Cortex, CI/CD, Git, Snowflake, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec41bc9f14435c5</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb623d0cc92d7a9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III: Backend C#</t>
+          <t>Associate Engineer - DevSecOps</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Exelixis</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, MySQL, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc6bd5f5982957</t>
+          <t>https://www.indeed.com/viewjob?jk=b03bceb651c00149</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Meridian: Full-Stack Engineer (Mid-level)</t>
+          <t>Software Engineer (Contractor)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>aVB</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Copilot, S3, CI/CD, GitHub Actions, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b03537494c4eccb</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e75e2f4f162f32</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MHK TECH</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, Synapse, CI/CD, GitHub Actions, Git, Databricks, SQL, R, Scala</t>
+          <t>RAG, Copilot, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02c0599e49eb558</t>
+          <t>https://www.indeed.com/viewjob?jk=50e2d3d07ecf5ad8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Katalyst Healthcares &amp; Life Sciences</t>
+          <t>Kalmbach Feeds</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Upper Sandusky, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Git, Databricks, Python, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f8cc3984a1b20d6</t>
+          <t>https://www.indeed.com/viewjob?jk=7815c035f0c767f2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Sciences</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Power BI, Python, R, Scala, Optimization</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Terraform, Databricks, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,59 +1861,59 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7196258be6af184b</t>
+          <t>https://www.indeed.com/viewjob?jk=59ec569330437bcf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Sciences</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Power BI, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c7e3534472f458</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf6f03f04ecc251</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tech Int Eng II</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>University of Wisconsin</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R</t>
+          <t>Data Scientist, RAG, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee1f39640dec75c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6a2b69bfdbc3f2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Intelligent Operations Team - Quant Analytics Senior Associate</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Scala, Optimization</t>
+          <t>RAG, XGBoost, LightGBM, Git, Snowflake, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=168c9d8374ad2930</t>
+          <t>https://www.indeed.com/viewjob?jk=c6a005e625656ca2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Advertiser Growth</t>
+          <t>Data Science Advisor - Hybrid</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Kafka, R, Java, Scala, Optimization, A/B Testing</t>
+          <t>Generative AI, TensorFlow, PyTorch, Tableau, Python, SQL, R, Scala, Bayesian</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1816e379c885a1a4</t>
+          <t>https://www.indeed.com/viewjob?jk=b5250527d28118b9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Advertiser Growth</t>
+          <t>Data Science Advisor - Hybrid</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Kafka, R, Java, Scala, Optimization, A/B Testing</t>
+          <t>Generative AI, TensorFlow, PyTorch, Tableau, Python, SQL, R, Scala, Bayesian</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f6d7061dd353756</t>
+          <t>https://www.indeed.com/viewjob?jk=abd88668187dadf8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Advertiser Growth</t>
+          <t>Data Science Advisor - Hybrid</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Kafka, R, Java, Scala, Optimization, A/B Testing</t>
+          <t>Generative AI, TensorFlow, PyTorch, Tableau, Python, SQL, R, Scala, Bayesian</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74473b4f136b60e2</t>
+          <t>https://www.indeed.com/viewjob?jk=f642141c6b97fcd5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Science Advisor - Hybrid</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Essentia Health</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Duluth, MN, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Data Lake, Apache Airflow, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, TensorFlow, PyTorch, Tableau, Python, SQL, R, Scala, Bayesian</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=978f98f416afa0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=aab9284d75566177</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Technology Co-Founder</t>
+          <t>SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>USA Quality Staffing INC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Lake, CI/CD, GitHub Actions, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,252 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f15e76bf8e4943f</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Charles Schwab</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=691c2ebdd97e0c2f</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>NerdWallet</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=abd40a840fd50a30</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Data Science Advisor - Hybrid</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>The Cigna Group</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Generative AI, TensorFlow, PyTorch, Tableau, Python, SQL, R, Scala, Bayesian</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d006a4f92936c0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Data Scientist I - Python and SQL</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>NORC at the University of Chicago</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, Git, Databricks, Hadoop, Python, SQL, R, Bayesian</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92a7df555c0fc9ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>AI-Native Application Software Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>One Park Financial</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Git, MongoDB, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4917230adfca94b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>AI-Native Application Software Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>One Park Financial</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Git, MongoDB, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16c52ad3eba395b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Sr. Software Developer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Super Micro Computer, Inc.</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>RAG, S3, Jenkins, Hadoop, MySQL, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e64a00f0a1a2ab18</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f57a5ba4b55368</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-29.xlsx
+++ b/daily_matches/job_matches_2026-09-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>Karoo Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Athena, Kinesis, Docker, Git, Snowflake, Kafka, Hadoop</t>
+          <t>RAG, S3, Athena, Redshift, BigQuery, Data Lake, Apache Airflow, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96ed04a9d166985</t>
+          <t>https://www.indeed.com/viewjob?jk=8150f9e8b835ffb3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Relativity</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>Copilot, Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423eda1e0efbb045</t>
+          <t>https://www.indeed.com/viewjob?jk=6a6d0a91a10a1715</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Distributed Systems Engineer, Energy</t>
+          <t>Full-stack Engineer 4 (Distributed data &amp; AWS) (Cloud Operations Resilience Engineering)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, Hadoop, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a63e864705cad81</t>
+          <t>https://www.indeed.com/viewjob?jk=f43423f60faa323d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Software Engineer - AI ML</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PySpark, Hadoop, MongoDB, NoSQL, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Keras, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a31aef3876037c</t>
+          <t>https://www.indeed.com/viewjob?jk=3199013e3b9315c8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python &amp; Java Full Stack Developer (AI-Assisted)</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65877c8eb122e7ac</t>
+          <t>https://www.indeed.com/viewjob?jk=b54c7cf7e0d49278</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Forward Development Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CrossCountry Consulting</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Pinecone, Prompt Engineering, Data Lake, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7425b7eaa6c55a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=73b249b48cff4978</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Enterprise Analytics</t>
+          <t>Technical Architect Wealth And Retirement</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Inland Real Estate Group of Companies, Inc.</t>
+          <t>Bridgenext</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Git, Kafka, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1fbedd6c9d0d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=4cbdbb96af073d71</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Enterprise Analytics</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Inland Real Estate Group of Companies, Inc.</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, LLaMA, Copilot, Prompt Engineering, MLflow, Docker, CI/CD, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=519dcdfdfb4bef2a</t>
+          <t>https://www.indeed.com/viewjob?jk=7723e6fd23ecca7e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Enterprise Analytics</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Inland Real Estate Group of Companies, Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1d075b9f067a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b43cbdd72bcba2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Baker Hughes</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a1910476c5d08e3</t>
+          <t>https://www.indeed.com/viewjob?jk=508764c031e252bf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Full-stack Engineer 4 (Go, AWS)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZT Systems</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, Git</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94fb3ecd34b2c14</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbf885ed4904a21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, MySQL, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02324287df1f2770</t>
+          <t>https://www.indeed.com/viewjob?jk=57a51ee9cdac73f1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer/AI Solution Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>W. L. Gore &amp; Associates</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Elkton, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, PostgreSQL, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c7a8b75d558d86a</t>
+          <t>https://www.indeed.com/viewjob?jk=4514ecc84233be42</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior SW Engineer, AI Automation</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dentsply Sirona</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3794a67a181956</t>
+          <t>https://www.indeed.com/viewjob?jk=9551dd95afdb1040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks Engineer - Contractor (contract)</t>
+          <t>Full-stack Engineer 4 (Go, AWS)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Data Lake, Snowflake, Databricks, PySpark, Kafka, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f788a895458b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=e44d3b7e0c07709d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Full Stack Engineer - 4 (JavaScript, TypeScript)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KBX</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d82ffb5eaa627d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=f67c359ae426c4af</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KBX</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e7dd4a9a7ed2c5</t>
+          <t>https://www.indeed.com/viewjob?jk=19873039025aa3c2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Data Platform Engineer</t>
+          <t>Full-stack Engineer 5 (Go, Python, Java)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Glue, Athena, Redshift, CI/CD, Terraform, Redshift, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fca4cdbad781b6fe</t>
+          <t>https://www.indeed.com/viewjob?jk=29aaf0f8edda59ec</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RightsLine</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Git, NoSQL, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355bd600a0ce4716</t>
+          <t>https://www.indeed.com/viewjob?jk=a3f599d1a2697280</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Consultant or Senior Consultant, Technical Solutions</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AVP, Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf1c610c653b6b3</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e11573274ef49</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 5 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Diabetes Association</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba066468e1bd0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=1b3c11f0e138eb84</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83646eeb4bc9897a</t>
+          <t>https://www.indeed.com/viewjob?jk=7374c6749391f2ff</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Full-stack Engineer 4 (Python, Java, Spring Boot)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Argonne National Laboratory</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lemont, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Git, PostgreSQL, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f00ff6ed18dfd67</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f77940dd9eb1d5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-stack Engineer 4 (Go &amp; Kubernetes) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, Kubernetes, CI/CD, Terraform, BigQuery, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63bbe79a14f6024</t>
+          <t>https://www.indeed.com/viewjob?jk=a0553ca4bc8ebe65</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Science Internship (Current PhD) - Summer 2027</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Neighbor</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Athena, Redshift, AKS, Redshift, Python, SQL, R, Hypothesis Testing</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216ebd6cfdfcddb6</t>
+          <t>https://www.indeed.com/viewjob?jk=32c94f784d741229</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CCB Risk Program Associate</t>
+          <t>Full-Stack Engineer 4 - AML Reporting</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Git, Hadoop, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27157e509862847c</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac04783f1f20e72</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-stack Engineer 4 (Backend &amp; API Development) (Cloud Operations Resilience Engineering)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, Kubernetes, CI/CD, Terraform, BigQuery, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=575d748548b1953f</t>
+          <t>https://www.indeed.com/viewjob?jk=94ef24bdc8f0aec2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Expert Data Scientist - Transmission Right of Way (ROW) Risk Analytics</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f9b69b4f17b5f1c</t>
+          <t>https://www.indeed.com/viewjob?jk=33e6ca9f48379974</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Enterprise AI Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f37f938e18bf5a</t>
+          <t>https://www.indeed.com/viewjob?jk=faf01c7d66890f7c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Snowflake, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Data Lake, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cb1e21fca446fa</t>
+          <t>https://www.indeed.com/viewjob?jk=05da5fe2d012b88a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Professional, Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Snowflake, Python, R, Java, Scala</t>
+          <t>S3, Glue, CI/CD, Terraform, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f54c5e3c17dace4d</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8c7cf8b092222e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Snowflake, Python, R, Java, Scala</t>
+          <t>RAG, Prompt Engineering, Cortex, CI/CD, GitHub Actions, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b78965e521bd63</t>
+          <t>https://www.indeed.com/viewjob?jk=d194b726c3ec9477</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Analyst II</t>
+          <t>Software Engineer III: Backend C#</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Education Analytics</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, MySQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4c4a90bc5d6ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9180a14620aa14</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, 3D Data</t>
+          <t>Junior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Medpace</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, MLflow, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, CI/CD, Terraform, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc119467d5eb85a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d80e20e6c49d29b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>University of Pennsylvania</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, Git, Snowflake, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, S3, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb623d0cc92d7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=602f835400ebe7a2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate Engineer - DevSecOps</t>
+          <t>Senior Data Analyst - Data Management &amp; BI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Exelixis</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Python, R, Java, Scala</t>
+          <t>RAG, Redshift, Snowflake, Databricks, Redshift, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03bceb651c00149</t>
+          <t>https://www.indeed.com/viewjob?jk=f0c613104583d041</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer (Contractor)</t>
+          <t>Data Engineer I - Data Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>aVB</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Copilot, S3, CI/CD, GitHub Actions, Git, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e75e2f4f162f32</t>
+          <t>https://www.indeed.com/viewjob?jk=b7daae54db1e425f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Engineer 4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50e2d3d07ecf5ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=7cdd180df03b18c7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Machine Learning Engineer 5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kalmbach Feeds</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Upper Sandusky, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7815c035f0c767f2</t>
+          <t>https://www.indeed.com/viewjob?jk=3ddc4f08c0dd4d6d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Bollinger Shipyards</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Raceland, LA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Terraform, Databricks, SQL, R, Scala</t>
+          <t>Synapse, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ec569330437bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=664254325a625205</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Systems Engineer, Database Infrastructure</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Git, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf6f03f04ecc251</t>
+          <t>https://www.indeed.com/viewjob?jk=aa56f4e5a735573a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Specialist Solutions Architect - AWS Infrastructure &amp; Platform</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Synapse, Terraform, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6a2b69bfdbc3f2</t>
+          <t>https://www.indeed.com/viewjob?jk=76c080f60278d6dc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Machine Learning Intelligent Operations Team - Quant Analytics Senior Associate</t>
+          <t>Specialist Solutions Architect - Azure Infrastructure &amp; Platform</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAG, XGBoost, LightGBM, Git, Snowflake, Tableau, Python, SQL, R</t>
+          <t>Synapse, Terraform, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6a005e625656ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=9d283def45f7dc44</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Science Advisor - Hybrid</t>
+          <t>Software Engineering Intern - S</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Generative AI, TensorFlow, PyTorch, Tableau, Python, SQL, R, Scala, Bayesian</t>
+          <t>Generative AI, RAG, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5250527d28118b9</t>
+          <t>https://www.indeed.com/viewjob?jk=802f86f64e322495</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Science Advisor - Hybrid</t>
+          <t>Ai Automation Expert</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Triple Group of Industries</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Generative AI, TensorFlow, PyTorch, Tableau, Python, SQL, R, Scala, Bayesian</t>
+          <t>LangChain, Prompt Engineering, PostgreSQL, MySQL, MongoDB, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd88668187dadf8</t>
+          <t>https://www.indeed.com/viewjob?jk=4394efb2e972fb5f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Science Advisor - Hybrid</t>
+          <t>Machine Learning Intern - S</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Generative AI, TensorFlow, PyTorch, Tableau, Python, SQL, R, Scala, Bayesian</t>
+          <t>Generative AI, TensorFlow, PyTorch, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,77 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f642141c6b97fcd5</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Data Science Advisor - Hybrid</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>The Cigna Group</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Bloomfield, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Generative AI, TensorFlow, PyTorch, Tableau, Python, SQL, R, Scala, Bayesian</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aab9284d75566177</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>SOFTWARE ENGINEER</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>USA Quality Staffing INC</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Data Lake, CI/CD, GitHub Actions, Git, Databricks, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f57a5ba4b55368</t>
+          <t>https://www.indeed.com/viewjob?jk=48654d5668b1d55c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-29.xlsx
+++ b/daily_matches/job_matches_2026-09-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Intern</t>
+          <t>Senior Data Engineer - Apartments.com - Irvine, CA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RAG, Gemini, Copilot, Prompt Engineering, S3, BigQuery, Data Lake, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0a75acda2378a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a53ace7c739bbef4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II - Apartments.com - Irvine, CA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Docker, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Gemini, Copilot, Prompt Engineering, S3, BigQuery, Data Lake, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc7c1c9088b36ce</t>
+          <t>https://www.indeed.com/viewjob?jk=a0ca5cc30971dc02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate AI/ML Engineer</t>
+          <t>Data Engineer (AWS &amp; Azure) - Contract-to-Hire</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cruz Street</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Vero Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, Git, Databricks, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, S3, Glue, Athena, Redshift, Synapse, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1cb11c12015007c</t>
+          <t>https://www.indeed.com/viewjob?jk=339fc28aca922522</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cricut</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>21.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, PyTorch, Glue, Data Lake, Docker, Git, Python</t>
+          <t>Data Scientist, Generative AI, RAG, S3, Glue, Redshift, Data Lake, Kinesis, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151ea1e60e7bac7b</t>
+          <t>https://www.indeed.com/viewjob?jk=0116d4b4ca656c94</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pittsburg, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Redshift, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=247c485b2435bbc9</t>
+          <t>https://www.indeed.com/viewjob?jk=ab0ee907185e5f01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Escaltion Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wiz Soluções</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, spaCy, MLflow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99563b0f31ddd24d</t>
+          <t>https://www.indeed.com/viewjob?jk=e34ff016d0be98fe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cricut</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Prompt Engineering, TensorFlow, PyTorch, XGBoost, MLflow, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b81ccfe00621caf</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fcc3fc97e62735</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist – Business &amp; Product</t>
+          <t>AI/ML Engineer Intern</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, BigQuery, CI/CD, Snowflake, BigQuery, Tableau, Python, SQL, R, Bayesian</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e6143540f18e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f7e1ef8e1fdbe0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Stf - E4</t>
+          <t>AI/ML Engineer Intern</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Docker, Jenkins, GitHub Actions, Git, R, Java, Optimization</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2106be124aec7e01</t>
+          <t>https://www.indeed.com/viewjob?jk=96d7c2108f3611f5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI/ML Engineer, Amazon Bedrock and AgentCore (Healthcare)</t>
+          <t>AI/ML Engineer Intern</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D9Tech Resources, LLC</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, FastAPI, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86795e2073c3310c</t>
+          <t>https://www.indeed.com/viewjob?jk=a94392d03faa7aff</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mohegan Sun</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uncasville, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Gemini, Copilot, BigQuery, Docker, Jenkins, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea2a5646dacca1b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8730847460692f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Security Engineer</t>
+          <t>Senior Java Engineer – Agentic AI Driven Development</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=005adfced45035be</t>
+          <t>https://www.indeed.com/viewjob?jk=fadbf39a366c1e1a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fullstack Engineer (PHP/Symfony)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ProFocus</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, PostgreSQL, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, MLflow, Docker, CI/CD, GitHub Actions, Git, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41026573fe342c71</t>
+          <t>https://www.indeed.com/viewjob?jk=aaff853ea9e0984e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Manufacturing Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Itron</t>
+          <t>All IT Solutions LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>West Union, SC, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a74cf7f369ce28b</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb630341625dadf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Cloud Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Terracon Consultants Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, TensorFlow, PyTorch, YOLO, Git, Python, R</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,42 +986,2177 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618ae58e454e4cef</t>
+          <t>https://www.indeed.com/viewjob?jk=f31525221f5ef980</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer (Frontend)</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gridline</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=660e2cf474b4e061</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Engineer 4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98b9323fde0e076c</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Engineer Senior | Hybrid</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Allianz</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, MLflow, Kubernetes, CI/CD, GitHub Actions, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e49db045a45c992</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Engineer (Generative AI &amp; Healthcare Data)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Altarum</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, MLflow, CI/CD, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f49e9b26d98bb56</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Platform</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, Kubernetes, Snowflake, Kafka, Hadoop, PostgreSQL, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83176228c53939c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Platform</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, Kubernetes, Snowflake, Kafka, Hadoop, PostgreSQL, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9c93b5fec88654f</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (contract)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Docker, Kubernetes, CI/CD, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9f06e9c1174ecaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Developer / Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, S3, Glue, Athena, Data Lake, CI/CD, Git, PySpark, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=925e167443880f65</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Copilot, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5865d81e8fd72c5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Developer II, Full Stack</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RS21: A Data Science and Visualization Company</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Terraform, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a21bf6e7428ba253</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, NoSQL, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe97c58bd1f9ed9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, NoSQL, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae5f97b462b22e62</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer VNDLY</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Mason, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94bdca5e980fb5ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Architect - Healthcare Insights, Revenue Cycle</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Huron Consulting Group</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Pinecone, CI/CD, Snowflake, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b58dd53022f160e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Architect - Healthcare Insights, Pharmacy</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Huron Consulting Group</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Pinecone, CI/CD, Snowflake, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cae3580058d6b9fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer 4 (Nodejs, Angularjs, Java)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b68e3f744cf85a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4 (Cyber)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50df5c630173a79e</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5 (Cyber)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ff744ea970f680d</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=544c5bd52b84d1f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Technology I</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>North Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Git, MongoDB, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8e935360a6c84ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>American Lung Association</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a7ef180f361a4b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Southern Hobby Distribution</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Cortex, S3, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb16d38559fc0b69</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>University of Colorado</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Aurora, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, CI/CD, Git, Databricks, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=551c49c9aa5e5584</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AI/ML Software Engineering - Talent Pipeline</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>IQware</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, PyTorch, FastAPI, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4f75954cc33611c</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Consultant - Forward Deployed AI Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Arthur D. Little</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Hugging Face, PyTorch, Git, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2dc7f932a984d8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Applied AI Scientist IV</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CareSource</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51bb3fca8294acee</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Meijer</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, Copilot, TensorFlow, PyTorch, Azure ML, Synapse, Databricks, PySpark, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adc5d23ecbf9a0d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89f81df1171c021f</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=837634850a0203cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d24d4daaf9008859</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdb8fbc8bd0b2d0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77b9ed43e8be6469</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44589587fe108d0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>DocuSign</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c49dd2e3d5e4e05</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Excel Group</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a8aae08c3d638fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a444cf403547dd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d82ce7964f047ad8</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AI Agent Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Juno Beach, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a25840c68f8bf4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AMH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>CI/CD, Databricks, Kafka, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34ed24d87685f8d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Software Developer, Full Stack</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RS21: A Data Science and Visualization Company</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Data Scientist, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Terraform, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcef4ca76cf82651</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Full stack Java &amp; React Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, MongoDB, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b529783decc62227</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Full-stack Java &amp; React Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, MongoDB, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ce81ee223393948</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Software Engineer II - MuleSoft</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, CI/CD, Jenkins, Git, MongoDB, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=991218d731d3aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Bitsight</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d92116478d1d3eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Hoboken, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Dataflow, Tableau, Power BI, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61855a440af2cf12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Consultant, AI Transformation Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Infinitive Inc</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fd661ef0b1e39c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, CI/CD, Terraform, MySQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=185c18e26821b931</t>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, R, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e01673a28815832</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Associate Engineer / Senior Associate Engineer, Systems Design &amp; Integration</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Spear Bio</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Woburn, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=beef0da5ab55a0c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Applied Research Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>HighArc</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, Keras, FastAPI, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5e0b4bf97ff36aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer (Front-end)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Mad Mobile</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bba7e5c4edf6a487</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Enterprise AI Architect</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>California Institute of Technology</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Pasadena, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad5036bbdf9b8128</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>NIKE, Inc. AI &amp; Machine Learning, Innovation Graduate Internship</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NIKE</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Beaverton, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, OpenCV, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e44bc0e47b5c5ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Intuitive (Intuitive Surgical)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=beb29512b840f203</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Advisor Product Developer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Gainwell Technologies LLC</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Glue, CI/CD, Terraform, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4db162f3191da93b</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Software Engineer Sys 2</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Lam Research</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Generative AI, FAISS, Prompt Engineering, Docker, Kubernetes, CI/CD, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af016da52ad0d82f</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Data Engineer Senior (Python/SQL)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PNC Financial Services Group</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Lakewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbe5f4121021f1f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Databricks, Python, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=456b50afd5101973</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Wakefield, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Databricks, Python, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ed26db14f16ddf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Westminster, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Databricks, Python, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afefce60e98dfce5</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Databricks, Python, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e09f8d387e543b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Databricks, Python, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9719593d70f2d71</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>TKC Holdings</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Dataflow, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0839459de9ce2dea</t>
         </is>
       </c>
     </row>
